--- a/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProdStatusRegist001.xlsx
+++ b/tams-svreport-parent/tams-svreport/src/main/resources/tpl/ProdStatusRegist001.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28665" windowHeight="12615"/>
+    <workbookView windowWidth="18530" windowHeight="7130"/>
   </bookViews>
   <sheets>
     <sheet name="产品状态登记" sheetId="1" r:id="rId1"/>
     <sheet name="填写说明" sheetId="2" r:id="rId2"/>
+    <sheet name="币种填写规则" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t>产品状态登记</t>
   </si>
@@ -81,24 +82,574 @@
   <si>
     <t>2.必填要素请参照《数据元规范》。</t>
   </si>
+  <si>
+    <t>币种填写规则：代码，如：CNY</t>
+  </si>
+  <si>
+    <t>CNY 人民币</t>
+  </si>
+  <si>
+    <t>HKD 港元</t>
+  </si>
+  <si>
+    <t>USD 美元</t>
+  </si>
+  <si>
+    <t>EUR 欧元</t>
+  </si>
+  <si>
+    <t>JPY 日元</t>
+  </si>
+  <si>
+    <t>MOP 澳门元</t>
+  </si>
+  <si>
+    <t>CHF 瑞士法郎</t>
+  </si>
+  <si>
+    <t>GBP 英镑</t>
+  </si>
+  <si>
+    <t>RUB 俄罗斯卢布</t>
+  </si>
+  <si>
+    <t>CAD 加拿大元</t>
+  </si>
+  <si>
+    <t>DKK 丹麦克朗</t>
+  </si>
+  <si>
+    <t>AUD 澳大利亚元</t>
+  </si>
+  <si>
+    <t>SEK 瑞典克朗</t>
+  </si>
+  <si>
+    <t>SGD 新加坡元</t>
+  </si>
+  <si>
+    <t>TWD 新台币</t>
+  </si>
+  <si>
+    <t>AED 阿拉伯联合酋长国迪尔汗</t>
+  </si>
+  <si>
+    <t>AFN 阿富汗阿富汗尼</t>
+  </si>
+  <si>
+    <t>ALL 阿尔巴尼亚列克</t>
+  </si>
+  <si>
+    <t>AMD 亚美尼亚德拉姆</t>
+  </si>
+  <si>
+    <t>ANG 荷属安的列斯盾</t>
+  </si>
+  <si>
+    <t>AOA 安哥拉宽扎</t>
+  </si>
+  <si>
+    <t>ARS 阿根廷比索</t>
+  </si>
+  <si>
+    <t>AWG 阿鲁巴弗罗林</t>
+  </si>
+  <si>
+    <t>AZN 阿塞拜疆马纳特</t>
+  </si>
+  <si>
+    <t>BAM 波斯尼亚和黑塞哥维那可兑换马克</t>
+  </si>
+  <si>
+    <t>BBD 巴巴多斯元</t>
+  </si>
+  <si>
+    <t>BDT 孟加拉塔卡</t>
+  </si>
+  <si>
+    <t>BGN 保加利亚列弗</t>
+  </si>
+  <si>
+    <t>BHD 巴林第纳尔</t>
+  </si>
+  <si>
+    <t>BIF 布隆迪法郎</t>
+  </si>
+  <si>
+    <t>BMD 百慕大元</t>
+  </si>
+  <si>
+    <t>BND 文莱元</t>
+  </si>
+  <si>
+    <t>BOB 玻利维亚诺</t>
+  </si>
+  <si>
+    <t>BOV 玻利维亚Mvdol基金</t>
+  </si>
+  <si>
+    <t>BRL 巴西雷亚尔</t>
+  </si>
+  <si>
+    <t>BSD 巴哈马元</t>
+  </si>
+  <si>
+    <t>BTN 不丹努扎姆</t>
+  </si>
+  <si>
+    <t>BWP 博茨瓦纳普拉</t>
+  </si>
+  <si>
+    <t>BYR 白俄罗斯卢布</t>
+  </si>
+  <si>
+    <t>BZD 伯利兹元</t>
+  </si>
+  <si>
+    <t>CDF 刚果民主共和国刚果法郎</t>
+  </si>
+  <si>
+    <t>CHE WIR欧元</t>
+  </si>
+  <si>
+    <t>CHW WIR法郎</t>
+  </si>
+  <si>
+    <t>CLF 智利UF基金</t>
+  </si>
+  <si>
+    <t>CLP 智利比索</t>
+  </si>
+  <si>
+    <t>COP 哥伦比亚比索</t>
+  </si>
+  <si>
+    <t>COU 哥伦比亚UVR基金</t>
+  </si>
+  <si>
+    <t>CRC 哥斯达黎加科朗</t>
+  </si>
+  <si>
+    <t>CUC 古巴可兑换比索</t>
+  </si>
+  <si>
+    <t>CUP 古巴比索</t>
+  </si>
+  <si>
+    <t>CVE 佛得角埃斯库多</t>
+  </si>
+  <si>
+    <t>CZK 捷克克朗</t>
+  </si>
+  <si>
+    <t>DJF 吉布提法郎</t>
+  </si>
+  <si>
+    <t>DOP 多米尼加比索</t>
+  </si>
+  <si>
+    <t>DZD 阿尔及利亚第纳尔</t>
+  </si>
+  <si>
+    <t>EGP 埃及镑</t>
+  </si>
+  <si>
+    <t>ERN 厄立特里亚纳克法</t>
+  </si>
+  <si>
+    <t>ETB 埃塞俄比亚比尔</t>
+  </si>
+  <si>
+    <t>FJD 斐济元</t>
+  </si>
+  <si>
+    <t>FKP 福克兰镑</t>
+  </si>
+  <si>
+    <t>GEL 格鲁吉亚拉里</t>
+  </si>
+  <si>
+    <t>GHS 加纳塞地</t>
+  </si>
+  <si>
+    <t>GIP 直布罗陀镑</t>
+  </si>
+  <si>
+    <t>GMD 冈比亚达拉西</t>
+  </si>
+  <si>
+    <t>GNF 几内亚法郎</t>
+  </si>
+  <si>
+    <t>GTQ 危地马拉格查尔</t>
+  </si>
+  <si>
+    <t>GYD 圭亚那元</t>
+  </si>
+  <si>
+    <t>HNL 洪都拉斯伦皮拉</t>
+  </si>
+  <si>
+    <t>HRK 克罗地亚库纳</t>
+  </si>
+  <si>
+    <t>HTG 海地古德</t>
+  </si>
+  <si>
+    <t>HUF 匈牙利福林</t>
+  </si>
+  <si>
+    <t>IDR 印度尼西亚卢比</t>
+  </si>
+  <si>
+    <t>ILS 以色列新谢克尔</t>
+  </si>
+  <si>
+    <t>INR 印度卢比</t>
+  </si>
+  <si>
+    <t>IQD 伊拉克第纳尔</t>
+  </si>
+  <si>
+    <t>IRR 伊朗里亚尔</t>
+  </si>
+  <si>
+    <t>ISK 冰岛克朗</t>
+  </si>
+  <si>
+    <t>JMD 牙买加元</t>
+  </si>
+  <si>
+    <t>JOD 约旦第纳尔</t>
+  </si>
+  <si>
+    <t>KES 肯尼亚先令</t>
+  </si>
+  <si>
+    <t>KGS 吉尔吉斯斯坦索姆</t>
+  </si>
+  <si>
+    <t>KHR 柬埔寨瑞尔</t>
+  </si>
+  <si>
+    <t>KMF 科摩罗法郎</t>
+  </si>
+  <si>
+    <t>KPW 朝鲜元</t>
+  </si>
+  <si>
+    <t>KRW 韩元</t>
+  </si>
+  <si>
+    <t>KWD 科威特第纳尔</t>
+  </si>
+  <si>
+    <t>KYD 开曼群岛元</t>
+  </si>
+  <si>
+    <t>KZT 哈萨克斯坦坚戈</t>
+  </si>
+  <si>
+    <t>LAK 老挝基普</t>
+  </si>
+  <si>
+    <t>LBP 黎巴嫩镑</t>
+  </si>
+  <si>
+    <t>LKR 斯里兰卡卢比</t>
+  </si>
+  <si>
+    <t>LRD 利比里亚元</t>
+  </si>
+  <si>
+    <t>LSL 莱索托洛蒂</t>
+  </si>
+  <si>
+    <t>LYD 利比亚第纳尔</t>
+  </si>
+  <si>
+    <t>MAD 摩洛哥迪拉姆</t>
+  </si>
+  <si>
+    <t>MDL 摩尔多瓦列伊</t>
+  </si>
+  <si>
+    <t>MGA 马达加斯加阿里亚里</t>
+  </si>
+  <si>
+    <t>MKD 马其顿代纳尔</t>
+  </si>
+  <si>
+    <t>MMK 缅甸元</t>
+  </si>
+  <si>
+    <t>MNT 蒙古图格里克</t>
+  </si>
+  <si>
+    <t>MRO 毛里塔尼亚乌吉亚</t>
+  </si>
+  <si>
+    <t>MUR 毛里求斯卢比</t>
+  </si>
+  <si>
+    <t>MVR 马尔代夫拉菲亚</t>
+  </si>
+  <si>
+    <t>MWK 马拉维克瓦查</t>
+  </si>
+  <si>
+    <t>MXN 墨西哥比索</t>
+  </si>
+  <si>
+    <t>MXV 墨西哥UDI基金</t>
+  </si>
+  <si>
+    <t>MYR 马来西亚令吉</t>
+  </si>
+  <si>
+    <t>MZN 莫桑比克梅蒂卡尔</t>
+  </si>
+  <si>
+    <t>NAD 纳米比亚元</t>
+  </si>
+  <si>
+    <t>NGN 尼日利亚奈拉</t>
+  </si>
+  <si>
+    <t>NIO 尼加拉瓜科多巴</t>
+  </si>
+  <si>
+    <t>NOK 挪威克朗</t>
+  </si>
+  <si>
+    <t>NPR 尼泊尔卢比</t>
+  </si>
+  <si>
+    <t>NZD 新西兰元</t>
+  </si>
+  <si>
+    <t>OMR 阿曼里亚尔</t>
+  </si>
+  <si>
+    <t>PAB 巴拿马巴波亚</t>
+  </si>
+  <si>
+    <t>PEN 秘鲁新索尔</t>
+  </si>
+  <si>
+    <t>PGK 巴布亚新几内亚基那</t>
+  </si>
+  <si>
+    <t>PHP 菲律宾比索</t>
+  </si>
+  <si>
+    <t>PKR 巴基斯坦卢比</t>
+  </si>
+  <si>
+    <t>PLN 波兰兹罗提</t>
+  </si>
+  <si>
+    <t>PYG 巴拉圭瓜拉尼</t>
+  </si>
+  <si>
+    <t>QAR 卡塔尔里亚尔</t>
+  </si>
+  <si>
+    <t>RON 罗马尼亚列伊</t>
+  </si>
+  <si>
+    <t>RSD 塞尔维亚第纳尔</t>
+  </si>
+  <si>
+    <t>RWF 卢旺达法郎</t>
+  </si>
+  <si>
+    <t>SAR 沙特里亚尔</t>
+  </si>
+  <si>
+    <t>SBD 所罗门群岛元</t>
+  </si>
+  <si>
+    <t>SCR 塞舌尔卢比</t>
+  </si>
+  <si>
+    <t>SDG 苏丹镑</t>
+  </si>
+  <si>
+    <t>SHP 圣赫勒拿镑</t>
+  </si>
+  <si>
+    <t>SLL 塞拉利昂利昂</t>
+  </si>
+  <si>
+    <t>SOS 索马里先令</t>
+  </si>
+  <si>
+    <t>SRD 苏里南元</t>
+  </si>
+  <si>
+    <t>SSP 南苏丹镑</t>
+  </si>
+  <si>
+    <t>STD 圣多美和普林西比多布拉</t>
+  </si>
+  <si>
+    <t>SVC 萨尔瓦多科朗</t>
+  </si>
+  <si>
+    <t>SYP 叙利亚镑</t>
+  </si>
+  <si>
+    <t>SZL 斯威士兰里兰吉尼</t>
+  </si>
+  <si>
+    <t>THB 泰铢</t>
+  </si>
+  <si>
+    <t>TJS 塔吉克斯坦索莫尼</t>
+  </si>
+  <si>
+    <t>TMT 土库曼斯坦马纳特</t>
+  </si>
+  <si>
+    <t>TND 突尼斯第纳尔</t>
+  </si>
+  <si>
+    <t>TOP 汤加潘加</t>
+  </si>
+  <si>
+    <t>TRY 土耳其里拉</t>
+  </si>
+  <si>
+    <t>TTD 特立尼达和多巴哥元</t>
+  </si>
+  <si>
+    <t>TZS 坦桑尼亚先令</t>
+  </si>
+  <si>
+    <t>UAH 乌克兰格里夫尼亚</t>
+  </si>
+  <si>
+    <t>UGX 乌干达先令</t>
+  </si>
+  <si>
+    <t>USN 美元翌日基金</t>
+  </si>
+  <si>
+    <t>UYI 乌拉圭URUIURUI基金</t>
+  </si>
+  <si>
+    <t>UYU 乌拉圭比索</t>
+  </si>
+  <si>
+    <t>UZS 乌兹别克斯坦苏姆</t>
+  </si>
+  <si>
+    <t>VEF 委内瑞拉博利瓦</t>
+  </si>
+  <si>
+    <t>VND 越南盾</t>
+  </si>
+  <si>
+    <t>VUV 瓦努阿图瓦图</t>
+  </si>
+  <si>
+    <t>WST 萨摩亚塔拉</t>
+  </si>
+  <si>
+    <t>XAF 中非金融合作法郎（中非法郎）</t>
+  </si>
+  <si>
+    <t>XAG 银（一盎司）</t>
+  </si>
+  <si>
+    <t>XAU 金（一盎司）</t>
+  </si>
+  <si>
+    <t>XBA 欧洲混合单位（债券市场单位）</t>
+  </si>
+  <si>
+    <t>XBB 欧洲货币单位（债券市场单位）</t>
+  </si>
+  <si>
+    <t>XBC 欧洲计算单位9（债券市场单位）</t>
+  </si>
+  <si>
+    <t>XBD 欧洲计算单位17（债券市场单位）</t>
+  </si>
+  <si>
+    <t>XCD 东加勒比元</t>
+  </si>
+  <si>
+    <t>XDR 特别提款权（国际货币基金）</t>
+  </si>
+  <si>
+    <t>XOF 非洲金融共同体法郎（西非法郎）</t>
+  </si>
+  <si>
+    <t>XPD 钯（一盎司）</t>
+  </si>
+  <si>
+    <t>XPF 太平洋法兰西共同体法郎（CFP法郎）</t>
+  </si>
+  <si>
+    <t>XPT 铂（一盎司）</t>
+  </si>
+  <si>
+    <t>XSU 厄瓜多尔苏克雷</t>
+  </si>
+  <si>
+    <t>XTS 为测试保留的代码</t>
+  </si>
+  <si>
+    <t>XUA 非洲开发银行账户单位</t>
+  </si>
+  <si>
+    <t>XXX 非货币交易单位</t>
+  </si>
+  <si>
+    <t>YER 也门里亚尔</t>
+  </si>
+  <si>
+    <t>ZAR 南非兰特</t>
+  </si>
+  <si>
+    <t>ZMW 赞比亚克瓦查</t>
+  </si>
+  <si>
+    <t>ZWL 津巴布韦元</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="宋体"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
@@ -135,29 +686,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="宋体"/>
@@ -173,77 +701,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -272,10 +738,89 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color indexed="8"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -299,25 +844,163 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -329,150 +1012,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -484,12 +1029,49 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -509,21 +1091,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -534,24 +1101,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -573,11 +1122,33 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,8 +1171,19 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -613,10 +1195,10 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -625,150 +1207,155 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
@@ -778,10 +1365,10 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
@@ -841,6 +1428,11 @@
     <cellStyle name="常规 2" xfId="49"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1096,57 +1688,56 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2" outlineLevelCol="6"/>
   <cols>
-    <col min="1" max="1" width="18.6333333333333" style="5" customWidth="1"/>
-    <col min="2" max="2" width="19.1333333333333" style="5" customWidth="1"/>
-    <col min="3" max="3" width="26.6333333333333" style="5" customWidth="1"/>
-    <col min="4" max="4" width="21.25" style="5" customWidth="1"/>
-    <col min="5" max="5" width="16.8833333333333" style="5" customWidth="1"/>
-    <col min="6" max="6" width="18.6333333333333" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="18.6363636363636" style="10" customWidth="1"/>
+    <col min="2" max="2" width="19.1363636363636" style="10" customWidth="1"/>
+    <col min="3" max="3" width="26.6363636363636" style="10" customWidth="1"/>
+    <col min="4" max="4" width="21.2545454545455" style="10" customWidth="1"/>
+    <col min="5" max="5" width="16.8818181818182" style="10" customWidth="1"/>
+    <col min="6" max="6" width="18.6363636363636" style="10" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="10"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="1" ht="20.25" spans="1:6">
-      <c r="A1" s="6" t="s">
+    <row r="1" s="9" customFormat="1" ht="21" spans="1:6">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" s="4" customFormat="1" spans="1:6">
-      <c r="A2" s="7" t="s">
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+    </row>
+    <row r="2" s="9" customFormat="1" spans="1:6">
+      <c r="A2" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="12" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="3" spans="7:7">
-      <c r="G3" s="8"/>
+      <c r="G3" s="13"/>
     </row>
   </sheetData>
   <sheetProtection password="EC2B" sheet="1" formatRows="0" insertRows="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0" objects="1"/>
@@ -1154,10 +1745,10 @@
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <dataValidations count="4">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="必须为n(15,2)格式" sqref="C2"/>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="必须为n(15,2)格式" sqref="C1 C7 C3:C6 C8:C1048576">
       <formula1>((LEN(C1)-IFERROR(FIND(".",C1,1),LEN(C1)))&lt;=2)*(LEN(ABS(INT(C1)))&lt;=13)*COUNT(RIGHT(C1,1))*IF(COUNT(LEFT(C1,1)),1,IF(LEFT(C1,1)="-",1,0))</formula1>
     </dataValidation>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" error="必须为n(15,2)格式" sqref="C2"/>
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" error="必须为n(8,5)格式" sqref="D1 D7 D3:D6 D8:D1048576">
       <formula1>((LEN(D1)-IFERROR(FIND(".",D1,1),LEN(D1)))&lt;=5)*(LEN(ABS(INT(D1)))&lt;=3)*COUNT(RIGHT(D1,1))*IF(COUNT(LEFT(D1,1)),1,IF(LEFT(D1,1)="-",1,0))</formula1>
     </dataValidation>
@@ -1169,27 +1760,27 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:A3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="62.625" style="1" customWidth="1"/>
-    <col min="2" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="62.6272727272727" style="6" customWidth="1"/>
+    <col min="2" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.25" spans="1:1">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="15" spans="1:1">
+      <c r="A1" s="7" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" ht="28.5" spans="1:1">
-      <c r="A2" s="3" t="s">
+    <row r="2" ht="30" spans="1:1">
+      <c r="A2" s="8" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="3" ht="14.25" spans="1:1">
-      <c r="A3" s="3" t="s">
+    <row r="3" ht="15" spans="1:1">
+      <c r="A3" s="8" t="s">
         <v>9</v>
       </c>
     </row>
@@ -1198,4 +1789,917 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:A179"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
+  <cols>
+    <col min="1" max="1" width="46.7545454545455" style="1" customWidth="1"/>
+    <col min="2" max="16381" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="4" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" ht="15" customHeight="1" spans="1:1">
+      <c r="A17" s="4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="1:1">
+      <c r="A26" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" s="4" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="4" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="42" ht="15" customHeight="1" spans="1:1">
+      <c r="A42" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" s="4" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" s="4" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" s="4" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" s="4" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" s="4" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" s="4" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" s="4" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" s="4" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" s="4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" s="4" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" s="4" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" s="4" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" s="4" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="4" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" s="4" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98" s="4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101" s="4" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103" s="4" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" s="4" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" s="4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" s="4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" s="4" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" s="4" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" s="4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112" s="4" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="4" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="4" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="4" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="4" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124" s="4" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" s="4" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" s="4" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128" s="4" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130" s="4" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131" s="4" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132" s="4" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134" s="4" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135" s="4" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="137" ht="15" customHeight="1" spans="1:1">
+      <c r="A137" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142" s="4" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146" s="4" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148" s="4" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150" s="4" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152" s="4" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155" s="4" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156" s="4" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158" s="4" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160" s="4" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161" s="4" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162" s="4" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165" s="4" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167" s="4" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168" s="4" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170" s="4" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171" s="4" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172" s="4" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection password="EC2B" sheet="1" objects="1"/>
+  <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="600" verticalDpi="600"/>
+  <headerFooter/>
+</worksheet>
 </file>